--- a/Umfrage/HCI-Vergleichsanalyse - Usability(1-18)_final.xlsx
+++ b/Umfrage/HCI-Vergleichsanalyse - Usability(1-18)_final.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\shkvm1\niclas$\Studium\Bachelorarbeit\Interviews\Tag 2 - 30.07.2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\shkvm1\niclas$\Studium\Bachelorarbeit\Interviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0E3B52-42E1-4B09-AE76-0139882E76F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4F7154-0225-4892-9848-EFD24C411E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,7 +212,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -256,16 +256,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
@@ -400,24 +397,6 @@
       <alignment horizontal="right" indent="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="right" indent="0"/>
     </dxf>
@@ -426,6 +405,24 @@
       <alignment horizontal="right" indent="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="right" indent="0"/>
     </dxf>
@@ -470,24 +467,6 @@
       <alignment horizontal="right" indent="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="right" indent="0"/>
     </dxf>
@@ -520,6 +499,24 @@
       <alignment horizontal="right" indent="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="right" indent="0"/>
     </dxf>
@@ -540,24 +537,6 @@
       <alignment horizontal="right" indent="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="right" indent="0"/>
     </dxf>
@@ -614,6 +593,24 @@
       <alignment horizontal="right" indent="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="right" indent="0"/>
     </dxf>
@@ -690,19 +687,19 @@
       <alignment horizontal="right" indent="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -724,41 +721,41 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FB6B2D3B-2DC5-4D5C-BB6A-F4001075657C}" name="Table13" displayName="Table13" ref="A1:Y19" totalsRowShown="0">
   <autoFilter ref="A1:Y19" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{6394682C-5878-474B-B400-F9425A1A73BB}" name="ID" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{70DB7C2E-9061-4196-AC81-194CB1174217}" name="Startzeit" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{D751AD38-4C04-40BE-B7F7-567DCC935964}" name="Fertigstellungszeit" dataDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{D5FF2EDA-2CF1-4D7F-A791-7EAF87E5D734}" name="E-Mail" dataDxfId="71"/>
-    <tableColumn id="5" xr3:uid="{5E50A04E-E5E3-452F-9849-F70DA86A8100}" name="Name" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{F7807DA0-8D18-4433-89AB-DAFD5B62D26F}" name="Zeitpunkt der letzten Änderung" dataDxfId="69"/>
-    <tableColumn id="7" xr3:uid="{17A698A6-910E-4229-B81A-D7EC2A195906}" name="Ich habe Erfahrung in der Benutzung von &quot;VMware vSphere&quot;." dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{D43F6CC4-6BB1-480E-83BA-15DE14477064}" name="Ich habe Erfahrung in der Benutzung von &quot;Nutanix NCI&quot;." dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{62F54E61-2B5E-49E6-8E53-BF2B17C39A52}" name="Ich habe Erfahrung in der Benutzung von &quot;Proxmox Virtual Environment&quot;." dataDxfId="66"/>
-    <tableColumn id="10" xr3:uid="{FA5E61AA-977D-40CD-B2B9-3D9576401773}" name="1.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="65"/>
-    <tableColumn id="11" xr3:uid="{B3BD439F-AE7D-4C28-BC43-A17DE2BF9769}" name="1.02: Ich fand das System unnötig komplex." dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{2A135A4D-2685-4271-8CC0-44CF9A14E9CF}" name="1.03: Ich fand das System einfach zu benutzen." dataDxfId="63"/>
-    <tableColumn id="13" xr3:uid="{657201DC-79FB-47C9-8D3B-3CCB06830C07}" name="1.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="62"/>
-    <tableColumn id="14" xr3:uid="{A3C0BDEC-7E7D-4E9D-8770-F4D35C564DFD}" name="1.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="61"/>
-    <tableColumn id="15" xr3:uid="{B73D8747-2D44-4FBD-AF20-9D4DAF746697}" name="1.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="60"/>
-    <tableColumn id="16" xr3:uid="{80E8D89C-0363-4EA5-949C-6FE1CACA903D}" name="1.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="59"/>
-    <tableColumn id="17" xr3:uid="{079073B4-D3AD-46F7-A355-0FCDAACA6B96}" name="1.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="58"/>
-    <tableColumn id="18" xr3:uid="{2D1B0A04-BB08-4B33-86C6-0A2A24F4223E}" name="1.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="57"/>
-    <tableColumn id="19" xr3:uid="{90935E8F-24A8-4B8A-A56F-C803D43D17DC}" name="1.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="56"/>
-    <tableColumn id="20" xr3:uid="{A0695211-1C78-478E-8D82-1EF24ED5CE05}" name="SUS Sum: 1,3,5,7,9" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{6394682C-5878-474B-B400-F9425A1A73BB}" name="ID" dataDxfId="113"/>
+    <tableColumn id="2" xr3:uid="{70DB7C2E-9061-4196-AC81-194CB1174217}" name="Startzeit" dataDxfId="112"/>
+    <tableColumn id="3" xr3:uid="{D751AD38-4C04-40BE-B7F7-567DCC935964}" name="Fertigstellungszeit" dataDxfId="111"/>
+    <tableColumn id="4" xr3:uid="{D5FF2EDA-2CF1-4D7F-A791-7EAF87E5D734}" name="E-Mail" dataDxfId="110"/>
+    <tableColumn id="5" xr3:uid="{5E50A04E-E5E3-452F-9849-F70DA86A8100}" name="Name" dataDxfId="109"/>
+    <tableColumn id="6" xr3:uid="{F7807DA0-8D18-4433-89AB-DAFD5B62D26F}" name="Zeitpunkt der letzten Änderung" dataDxfId="108"/>
+    <tableColumn id="7" xr3:uid="{17A698A6-910E-4229-B81A-D7EC2A195906}" name="Ich habe Erfahrung in der Benutzung von &quot;VMware vSphere&quot;." dataDxfId="107"/>
+    <tableColumn id="8" xr3:uid="{D43F6CC4-6BB1-480E-83BA-15DE14477064}" name="Ich habe Erfahrung in der Benutzung von &quot;Nutanix NCI&quot;." dataDxfId="106"/>
+    <tableColumn id="9" xr3:uid="{62F54E61-2B5E-49E6-8E53-BF2B17C39A52}" name="Ich habe Erfahrung in der Benutzung von &quot;Proxmox Virtual Environment&quot;." dataDxfId="105"/>
+    <tableColumn id="10" xr3:uid="{FA5E61AA-977D-40CD-B2B9-3D9576401773}" name="1.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="104"/>
+    <tableColumn id="11" xr3:uid="{B3BD439F-AE7D-4C28-BC43-A17DE2BF9769}" name="1.02: Ich fand das System unnötig komplex." dataDxfId="103"/>
+    <tableColumn id="12" xr3:uid="{2A135A4D-2685-4271-8CC0-44CF9A14E9CF}" name="1.03: Ich fand das System einfach zu benutzen." dataDxfId="102"/>
+    <tableColumn id="13" xr3:uid="{657201DC-79FB-47C9-8D3B-3CCB06830C07}" name="1.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="101"/>
+    <tableColumn id="14" xr3:uid="{A3C0BDEC-7E7D-4E9D-8770-F4D35C564DFD}" name="1.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="100"/>
+    <tableColumn id="15" xr3:uid="{B73D8747-2D44-4FBD-AF20-9D4DAF746697}" name="1.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="99"/>
+    <tableColumn id="16" xr3:uid="{80E8D89C-0363-4EA5-949C-6FE1CACA903D}" name="1.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="98"/>
+    <tableColumn id="17" xr3:uid="{079073B4-D3AD-46F7-A355-0FCDAACA6B96}" name="1.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="97"/>
+    <tableColumn id="18" xr3:uid="{2D1B0A04-BB08-4B33-86C6-0A2A24F4223E}" name="1.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="96"/>
+    <tableColumn id="19" xr3:uid="{90935E8F-24A8-4B8A-A56F-C803D43D17DC}" name="1.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="95"/>
+    <tableColumn id="20" xr3:uid="{A0695211-1C78-478E-8D82-1EF24ED5CE05}" name="SUS Sum: 1,3,5,7,9" dataDxfId="94">
       <calculatedColumnFormula>SUM(J2-1,L2-1,N2-1,P2-1,R2-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{4022AD86-2C1B-4868-896B-CC350040AD4D}" name="SUS -1 Sum:" dataDxfId="4">
+    <tableColumn id="21" xr3:uid="{4022AD86-2C1B-4868-896B-CC350040AD4D}" name="SUS -1 Sum:" dataDxfId="93">
       <calculatedColumnFormula>T2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{29F2026A-2008-4A29-83DB-0B764F888D58}" name="SUS Sum: 2,4,6,8,10" dataDxfId="3">
+    <tableColumn id="22" xr3:uid="{29F2026A-2008-4A29-83DB-0B764F888D58}" name="SUS Sum: 2,4,6,8,10" dataDxfId="92">
       <calculatedColumnFormula>SUM(5-K2,5-M2,5-O2,5-Q2,5-S2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{7C1C4E47-4F16-4D60-A6A8-04786BB50C3D}" name="SUS 5 - x Sum:" dataDxfId="2">
+    <tableColumn id="23" xr3:uid="{7C1C4E47-4F16-4D60-A6A8-04786BB50C3D}" name="SUS 5 - x Sum:" dataDxfId="91">
       <calculatedColumnFormula>V2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{9828EE0E-0EB8-4341-BFA6-1E72A9AA97D0}" name="Sum:" dataDxfId="1">
+    <tableColumn id="24" xr3:uid="{9828EE0E-0EB8-4341-BFA6-1E72A9AA97D0}" name="Sum:" dataDxfId="90">
       <calculatedColumnFormula>SUM(U2,W2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{590B0FDB-2D82-433B-942E-7A491ACAD15C}" name="Final SUS:" dataDxfId="0">
+    <tableColumn id="25" xr3:uid="{590B0FDB-2D82-433B-942E-7A491ACAD15C}" name="Final SUS:" dataDxfId="89">
       <calculatedColumnFormula>X2*2.5</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -770,41 +767,41 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BBF8FE80-F37F-4D4B-A22E-0A800EB53F8F}" name="Table14" displayName="Table14" ref="A1:Y19" totalsRowShown="0">
   <autoFilter ref="A1:Y19" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{9F1C3938-43B2-4816-B87B-FCAD39DBF7D4}" name="ID" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{F4AC677E-8AE7-4536-881A-782018D89505}" name="Startzeit" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{6D4374AE-FD68-4129-A650-C7C5391E6727}" name="Fertigstellungszeit" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{C8BDE7D1-BAEE-4E66-A248-13B66D58F1E9}" name="E-Mail" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{9363F041-BD3A-4DBE-AC3C-378B3A981949}" name="Name" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{F64087B8-6D4D-4B47-94C6-C03152CC6979}" name="Zeitpunkt der letzten Änderung" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{E57D2CBB-26CB-4005-9FCE-FA5E3B6A69C4}" name="Ich habe Erfahrung in der Benutzung von &quot;VMware vSphere&quot;." dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{CE911E5A-7016-42D3-A941-4480E9951927}" name="Ich habe Erfahrung in der Benutzung von &quot;Nutanix NCI&quot;." dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{6E81DE7A-385A-4093-8B28-C4157C19EFCD}" name="Ich habe Erfahrung in der Benutzung von &quot;Proxmox Virtual Environment&quot;." dataDxfId="47"/>
-    <tableColumn id="20" xr3:uid="{5903EB9E-7939-4121-B81B-C76D19C770FD}" name="2.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="46"/>
-    <tableColumn id="21" xr3:uid="{B4ADFEDF-D32A-4B91-9CD5-67FF2C16E95A}" name="2.02: Ich fand das System unnötig komplex." dataDxfId="45"/>
-    <tableColumn id="22" xr3:uid="{AB1ED675-CBC0-47FA-800C-2FFEAF790F0A}" name="2.03: Ich fand das System einfach zu benutzen." dataDxfId="44"/>
-    <tableColumn id="23" xr3:uid="{3F61170C-B782-481C-8AD4-6A92FE3E1495}" name="2.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="43"/>
-    <tableColumn id="24" xr3:uid="{FE0A761F-D88A-423D-9168-747C03EB484E}" name="2.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="42"/>
-    <tableColumn id="25" xr3:uid="{4B0833E9-3CD2-4F16-8A02-7C04882B5FCD}" name="2.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="41"/>
-    <tableColumn id="26" xr3:uid="{F032737A-9042-4DB3-BBED-9572E137133A}" name="2.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="40"/>
-    <tableColumn id="27" xr3:uid="{1B8A94D1-C84F-4221-A05E-4AEF052DDAE9}" name="2.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="39"/>
-    <tableColumn id="28" xr3:uid="{DFAF467C-8957-4A41-90E3-C66C18D8D78C}" name="2.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="38"/>
-    <tableColumn id="29" xr3:uid="{3D7003EF-2231-4C8B-9B4F-A4D4ECB9B940}" name="2.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{8900C801-6546-4CDB-8D08-B683B797C9D9}" name="SUS Sum: 1,3,5,7,9" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{9F1C3938-43B2-4816-B87B-FCAD39DBF7D4}" name="ID" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{F4AC677E-8AE7-4536-881A-782018D89505}" name="Startzeit" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{6D4374AE-FD68-4129-A650-C7C5391E6727}" name="Fertigstellungszeit" dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{C8BDE7D1-BAEE-4E66-A248-13B66D58F1E9}" name="E-Mail" dataDxfId="85"/>
+    <tableColumn id="5" xr3:uid="{9363F041-BD3A-4DBE-AC3C-378B3A981949}" name="Name" dataDxfId="84"/>
+    <tableColumn id="6" xr3:uid="{F64087B8-6D4D-4B47-94C6-C03152CC6979}" name="Zeitpunkt der letzten Änderung" dataDxfId="83"/>
+    <tableColumn id="7" xr3:uid="{E57D2CBB-26CB-4005-9FCE-FA5E3B6A69C4}" name="Ich habe Erfahrung in der Benutzung von &quot;VMware vSphere&quot;." dataDxfId="82"/>
+    <tableColumn id="8" xr3:uid="{CE911E5A-7016-42D3-A941-4480E9951927}" name="Ich habe Erfahrung in der Benutzung von &quot;Nutanix NCI&quot;." dataDxfId="81"/>
+    <tableColumn id="9" xr3:uid="{6E81DE7A-385A-4093-8B28-C4157C19EFCD}" name="Ich habe Erfahrung in der Benutzung von &quot;Proxmox Virtual Environment&quot;." dataDxfId="80"/>
+    <tableColumn id="20" xr3:uid="{5903EB9E-7939-4121-B81B-C76D19C770FD}" name="2.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="79"/>
+    <tableColumn id="21" xr3:uid="{B4ADFEDF-D32A-4B91-9CD5-67FF2C16E95A}" name="2.02: Ich fand das System unnötig komplex." dataDxfId="78"/>
+    <tableColumn id="22" xr3:uid="{AB1ED675-CBC0-47FA-800C-2FFEAF790F0A}" name="2.03: Ich fand das System einfach zu benutzen." dataDxfId="77"/>
+    <tableColumn id="23" xr3:uid="{3F61170C-B782-481C-8AD4-6A92FE3E1495}" name="2.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="76"/>
+    <tableColumn id="24" xr3:uid="{FE0A761F-D88A-423D-9168-747C03EB484E}" name="2.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="75"/>
+    <tableColumn id="25" xr3:uid="{4B0833E9-3CD2-4F16-8A02-7C04882B5FCD}" name="2.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="74"/>
+    <tableColumn id="26" xr3:uid="{F032737A-9042-4DB3-BBED-9572E137133A}" name="2.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="73"/>
+    <tableColumn id="27" xr3:uid="{1B8A94D1-C84F-4221-A05E-4AEF052DDAE9}" name="2.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="72"/>
+    <tableColumn id="28" xr3:uid="{DFAF467C-8957-4A41-90E3-C66C18D8D78C}" name="2.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="71"/>
+    <tableColumn id="29" xr3:uid="{3D7003EF-2231-4C8B-9B4F-A4D4ECB9B940}" name="2.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="70"/>
+    <tableColumn id="10" xr3:uid="{8900C801-6546-4CDB-8D08-B683B797C9D9}" name="SUS Sum: 1,3,5,7,9" dataDxfId="69">
       <calculatedColumnFormula>SUM(J2-1,L2-1,N2-1,P2-1,R2-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{83AE7F8A-EAB2-4A6C-AD37-6681C3C29160}" name="SUS -1 Sum:" dataDxfId="10">
+    <tableColumn id="11" xr3:uid="{83AE7F8A-EAB2-4A6C-AD37-6681C3C29160}" name="SUS -1 Sum:" dataDxfId="68">
       <calculatedColumnFormula>T2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9B496BDE-4253-43BB-8CE6-465CD0930600}" name="SUS Sum: 2,4,6,8,10" dataDxfId="9">
+    <tableColumn id="12" xr3:uid="{9B496BDE-4253-43BB-8CE6-465CD0930600}" name="SUS Sum: 2,4,6,8,10" dataDxfId="67">
       <calculatedColumnFormula>SUM(5-K2,5-M2,5-O2,5-Q2,5-S2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{11C8A643-B867-4B89-897C-36FDEF6DAE57}" name="SUS 5 - x Sum:" dataDxfId="8">
+    <tableColumn id="13" xr3:uid="{11C8A643-B867-4B89-897C-36FDEF6DAE57}" name="SUS 5 - x Sum:" dataDxfId="66">
       <calculatedColumnFormula>V2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{BCEE93AF-A595-4FBF-8667-8A06A8CFAAA0}" name="Sum:" dataDxfId="7">
+    <tableColumn id="14" xr3:uid="{BCEE93AF-A595-4FBF-8667-8A06A8CFAAA0}" name="Sum:" dataDxfId="65">
       <calculatedColumnFormula>SUM(U2,W2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{86696F50-334C-473F-9618-80F984A2957C}" name="Final SUS:" dataDxfId="6">
+    <tableColumn id="15" xr3:uid="{86696F50-334C-473F-9618-80F984A2957C}" name="Final SUS:" dataDxfId="64">
       <calculatedColumnFormula>X2*2.5</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -816,41 +813,41 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{98718EF4-D187-4314-B89A-0EF2F5D204EA}" name="Table15" displayName="Table15" ref="A1:Y19" totalsRowShown="0">
   <autoFilter ref="A1:Y19" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{854E85EC-B98A-4F4A-92D5-3E28C3685D48}" name="ID" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{1D5DEE29-D1B3-4FBB-BB6F-F887859824BF}" name="Startzeit" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{CA281DF8-0776-41F5-B555-EDD328983205}" name="Fertigstellungszeit" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{2D13C8B5-B5CF-45D7-8D21-495A14EB40F3}" name="E-Mail" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{1B06BD51-460E-4709-B4C2-471FA7395713}" name="Name" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{5A6C613C-552C-4C8D-8D09-AECE44CE785C}" name="Zeitpunkt der letzten Änderung" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{AE06DC11-E7E7-4F9D-AC4A-699D747AD9AA}" name="Ich habe Erfahrung in der Benutzung von &quot;VMware vSphere&quot;." dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{B8D493C1-BE0D-4B7E-B89F-C66F42B89F44}" name="Ich habe Erfahrung in der Benutzung von &quot;Nutanix NCI&quot;." dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{34B3885E-20CE-42A2-B7F9-A9018E28F51D}" name="Ich habe Erfahrung in der Benutzung von &quot;Proxmox Virtual Environment&quot;." dataDxfId="28"/>
-    <tableColumn id="30" xr3:uid="{522A4B3B-A16D-45B3-8722-1D139B672DD1}" name="3.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="27"/>
-    <tableColumn id="31" xr3:uid="{67548E91-EA6C-4D39-8A5C-BF1323C75703}" name="3.02: Ich fand das System unnötig komplex." dataDxfId="26"/>
-    <tableColumn id="32" xr3:uid="{FB2E3B1C-6162-46FC-8CFB-498D337BF07C}" name="3.03: Ich fand das System einfach zu benutzen." dataDxfId="25"/>
-    <tableColumn id="33" xr3:uid="{99B89D89-41CC-4A75-BBC1-2857B1DDB487}" name="3.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="24"/>
-    <tableColumn id="34" xr3:uid="{3B17F4D7-3EB0-4494-8ABE-6EAC3945AC9C}" name="3.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="23"/>
-    <tableColumn id="35" xr3:uid="{A379930C-332F-489F-9E2F-99FC0915322E}" name="3.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="22"/>
-    <tableColumn id="36" xr3:uid="{D641A68B-8E4B-4EB6-9381-4B1B8FC2FC3A}" name="3.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="21"/>
-    <tableColumn id="37" xr3:uid="{9D99E20B-736A-4B47-AF01-C440D6EC856B}" name="3.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="20"/>
-    <tableColumn id="38" xr3:uid="{0EEEACD1-71C4-478A-8C80-FE8650AB02EA}" name="3.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="19"/>
-    <tableColumn id="39" xr3:uid="{EFC30ADD-33C5-4782-99C8-088B1FE282BC}" name="3.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{B72E1752-F732-4645-93E8-19D0A221B728}" name="SUS Sum: 1,3,5,7,9" dataDxfId="17">
+    <tableColumn id="1" xr3:uid="{854E85EC-B98A-4F4A-92D5-3E28C3685D48}" name="ID" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{1D5DEE29-D1B3-4FBB-BB6F-F887859824BF}" name="Startzeit" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{CA281DF8-0776-41F5-B555-EDD328983205}" name="Fertigstellungszeit" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{2D13C8B5-B5CF-45D7-8D21-495A14EB40F3}" name="E-Mail" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{1B06BD51-460E-4709-B4C2-471FA7395713}" name="Name" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{5A6C613C-552C-4C8D-8D09-AECE44CE785C}" name="Zeitpunkt der letzten Änderung" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{AE06DC11-E7E7-4F9D-AC4A-699D747AD9AA}" name="Ich habe Erfahrung in der Benutzung von &quot;VMware vSphere&quot;." dataDxfId="57"/>
+    <tableColumn id="8" xr3:uid="{B8D493C1-BE0D-4B7E-B89F-C66F42B89F44}" name="Ich habe Erfahrung in der Benutzung von &quot;Nutanix NCI&quot;." dataDxfId="56"/>
+    <tableColumn id="9" xr3:uid="{34B3885E-20CE-42A2-B7F9-A9018E28F51D}" name="Ich habe Erfahrung in der Benutzung von &quot;Proxmox Virtual Environment&quot;." dataDxfId="55"/>
+    <tableColumn id="30" xr3:uid="{522A4B3B-A16D-45B3-8722-1D139B672DD1}" name="3.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="54"/>
+    <tableColumn id="31" xr3:uid="{67548E91-EA6C-4D39-8A5C-BF1323C75703}" name="3.02: Ich fand das System unnötig komplex." dataDxfId="53"/>
+    <tableColumn id="32" xr3:uid="{FB2E3B1C-6162-46FC-8CFB-498D337BF07C}" name="3.03: Ich fand das System einfach zu benutzen." dataDxfId="52"/>
+    <tableColumn id="33" xr3:uid="{99B89D89-41CC-4A75-BBC1-2857B1DDB487}" name="3.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="51"/>
+    <tableColumn id="34" xr3:uid="{3B17F4D7-3EB0-4494-8ABE-6EAC3945AC9C}" name="3.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="50"/>
+    <tableColumn id="35" xr3:uid="{A379930C-332F-489F-9E2F-99FC0915322E}" name="3.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="49"/>
+    <tableColumn id="36" xr3:uid="{D641A68B-8E4B-4EB6-9381-4B1B8FC2FC3A}" name="3.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="48"/>
+    <tableColumn id="37" xr3:uid="{9D99E20B-736A-4B47-AF01-C440D6EC856B}" name="3.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="47"/>
+    <tableColumn id="38" xr3:uid="{0EEEACD1-71C4-478A-8C80-FE8650AB02EA}" name="3.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="46"/>
+    <tableColumn id="39" xr3:uid="{EFC30ADD-33C5-4782-99C8-088B1FE282BC}" name="3.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{B72E1752-F732-4645-93E8-19D0A221B728}" name="SUS Sum: 1,3,5,7,9" dataDxfId="44">
       <calculatedColumnFormula>SUM(J2-1,L2-1,N2-1,P2-1,R2-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F57D593B-47CE-4073-A225-99A12CA1CE48}" name="SUS -1 Sum:" dataDxfId="16">
+    <tableColumn id="11" xr3:uid="{F57D593B-47CE-4073-A225-99A12CA1CE48}" name="SUS -1 Sum:" dataDxfId="43">
       <calculatedColumnFormula>T2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{0E427B2F-FA0F-403B-9858-D2018B23BD0C}" name="SUS Sum: 2,4,6,8,10" dataDxfId="15">
+    <tableColumn id="12" xr3:uid="{0E427B2F-FA0F-403B-9858-D2018B23BD0C}" name="SUS Sum: 2,4,6,8,10" dataDxfId="42">
       <calculatedColumnFormula>SUM(5-K2,5-M2,5-O2,5-Q2,5-S2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{6F02D53D-F5D4-4CB3-BAF1-EFFA4E6CA35B}" name="SUS 5 - x Sum:" dataDxfId="14">
+    <tableColumn id="13" xr3:uid="{6F02D53D-F5D4-4CB3-BAF1-EFFA4E6CA35B}" name="SUS 5 - x Sum:" dataDxfId="41">
       <calculatedColumnFormula>V2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{E6BD8FD4-B1D9-48E5-B26E-1EDBE7BF570C}" name="Sum:" dataDxfId="13">
+    <tableColumn id="14" xr3:uid="{E6BD8FD4-B1D9-48E5-B26E-1EDBE7BF570C}" name="Sum:" dataDxfId="40">
       <calculatedColumnFormula>SUM(U2,W2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{36FD5729-9FF4-47AE-9DB8-4D54A8FCD879}" name="Final SUS:" dataDxfId="12">
+    <tableColumn id="15" xr3:uid="{36FD5729-9FF4-47AE-9DB8-4D54A8FCD879}" name="Final SUS:" dataDxfId="39">
       <calculatedColumnFormula>X2*2.5</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -862,45 +859,45 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AM19" totalsRowShown="0">
   <autoFilter ref="A1:AM19" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="39">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="113"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Startzeit" dataDxfId="112"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Fertigstellungszeit" dataDxfId="111"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="E-Mail" dataDxfId="110"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="109"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Zeitpunkt der letzten Änderung" dataDxfId="108"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Ich habe Erfahrung in der Benutzung von &quot;VMware vSphere&quot;." dataDxfId="107"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Ich habe Erfahrung in der Benutzung von &quot;Nutanix NCI&quot;." dataDxfId="106"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Ich habe Erfahrung in der Benutzung von &quot;Proxmox Virtual Environment&quot;." dataDxfId="105"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="104"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="1.02: Ich fand das System unnötig komplex." dataDxfId="103"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="1.03: Ich fand das System einfach zu benutzen." dataDxfId="102"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="1.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="101"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="1.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="100"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="1.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="99"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="1.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="98"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="1.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="97"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="1.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="96"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="1.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="95"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="2.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="94"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2.02: Ich fand das System unnötig komplex." dataDxfId="93"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="2.03: Ich fand das System einfach zu benutzen." dataDxfId="92"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="2.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="91"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="2.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="90"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="2.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="89"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="2.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="88"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="2.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="87"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="2.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="86"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="2.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="85"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="3.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="84"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="3.02: Ich fand das System unnötig komplex." dataDxfId="83"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="3.03: Ich fand das System einfach zu benutzen." dataDxfId="82"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="3.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="81"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="3.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="80"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="3.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="79"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="3.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="78"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="3.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="77"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="3.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="76"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="3.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Startzeit" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Fertigstellungszeit" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="E-Mail" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Zeitpunkt der letzten Änderung" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Ich habe Erfahrung in der Benutzung von &quot;VMware vSphere&quot;." dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Ich habe Erfahrung in der Benutzung von &quot;Nutanix NCI&quot;." dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Ich habe Erfahrung in der Benutzung von &quot;Proxmox Virtual Environment&quot;." dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="1.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="1.02: Ich fand das System unnötig komplex." dataDxfId="28"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="1.03: Ich fand das System einfach zu benutzen." dataDxfId="27"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="1.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="26"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="1.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="25"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="1.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="24"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="1.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="23"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="1.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="1.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="1.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="20"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="2.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="19"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="2.02: Ich fand das System unnötig komplex." dataDxfId="18"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="2.03: Ich fand das System einfach zu benutzen." dataDxfId="17"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="2.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="16"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="2.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="15"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="2.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="14"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="2.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="13"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="2.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="12"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="2.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="11"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="2.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="10"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="3.01: Ich denke, dass ich das System gerne häufig benutzen würde." dataDxfId="9"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="3.02: Ich fand das System unnötig komplex." dataDxfId="8"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="3.03: Ich fand das System einfach zu benutzen." dataDxfId="7"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="3.04: Ich glaube, ich würde die Hilfe einer technisch versierten Person benötigen, um das System benutzen zu können." dataDxfId="6"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="3.05: Ich fand, die verschiedenen Funktionen in diesem System waren gut integriert." dataDxfId="5"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="3.06: Ich denke, das System enthielt zu viele Inkonsistenzen." dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="3.07: Ich kann mir vorstellen, dass die meisten Menschen den Umgang mit diesem System sehr schnell lernen." dataDxfId="3"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="3.08: Ich fand das System sehr umständlich zu nutzen._x000a_" dataDxfId="2"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="3.09: Ich fühlte mich bei der Benutzung des Systems sehr sicher._x000a_" dataDxfId="1"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="3.10: Ich musste eine Menge lernen, bevor ich anfangen konnte das System zu verwenden._x000a_" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1345,27 +1342,27 @@
       <c r="S2" s="3">
         <v>1</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="3">
         <f t="shared" ref="T2:T19" si="0">SUM(J2-1,L2-1,N2-1,P2-1,R2-1)</f>
         <v>15</v>
       </c>
-      <c r="U2" s="4">
+      <c r="U2" s="3">
         <f t="shared" ref="U2:U19" si="1">T2</f>
         <v>15</v>
       </c>
-      <c r="V2" s="4">
+      <c r="V2" s="3">
         <f t="shared" ref="V2:V19" si="2">SUM(5-K2,5-M2,5-O2,5-Q2,5-S2)</f>
         <v>18</v>
       </c>
-      <c r="W2" s="4">
+      <c r="W2" s="3">
         <f t="shared" ref="W2:W19" si="3">V2</f>
         <v>18</v>
       </c>
-      <c r="X2" s="4">
+      <c r="X2" s="3">
         <f t="shared" ref="X2:X19" si="4">SUM(U2,W2)</f>
         <v>33</v>
       </c>
-      <c r="Y2" s="4">
+      <c r="Y2" s="3">
         <f t="shared" ref="Y2:Y19" si="5">X2*2.5</f>
         <v>82.5</v>
       </c>
@@ -1423,27 +1420,27 @@
       <c r="S3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="4">
+      <c r="T3" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U3" s="4">
+      <c r="U3" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="V3" s="4">
+      <c r="V3" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="W3" s="4">
+      <c r="W3" s="3">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="X3" s="4">
+      <c r="X3" s="3">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="Y3" s="4">
+      <c r="Y3" s="3">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
@@ -1501,27 +1498,27 @@
       <c r="S4" s="3">
         <v>1</v>
       </c>
-      <c r="T4" s="4">
+      <c r="T4" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="V4" s="4">
+      <c r="V4" s="3">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="W4" s="4">
+      <c r="W4" s="3">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="X4" s="4">
+      <c r="X4" s="3">
         <f t="shared" si="4"/>
         <v>38</v>
       </c>
-      <c r="Y4" s="4">
+      <c r="Y4" s="3">
         <f t="shared" si="5"/>
         <v>95</v>
       </c>
@@ -1579,27 +1576,27 @@
       <c r="S5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U5" s="4">
+      <c r="U5" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="V5" s="4">
+      <c r="V5" s="3">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="W5" s="4">
+      <c r="W5" s="3">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="X5" s="4">
+      <c r="X5" s="3">
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="Y5" s="4">
+      <c r="Y5" s="3">
         <f t="shared" si="5"/>
         <v>92.5</v>
       </c>
@@ -1657,27 +1654,27 @@
       <c r="S6" s="3">
         <v>1</v>
       </c>
-      <c r="T6" s="4">
+      <c r="T6" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="V6" s="4">
+      <c r="V6" s="3">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="W6" s="4">
+      <c r="W6" s="3">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="X6" s="4">
+      <c r="X6" s="3">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="Y6" s="4">
+      <c r="Y6" s="3">
         <f t="shared" si="5"/>
         <v>77.5</v>
       </c>
@@ -1735,27 +1732,27 @@
       <c r="S7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T7" s="4">
+      <c r="T7" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V7" s="3">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="W7" s="4">
+      <c r="W7" s="3">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="X7" s="4">
+      <c r="X7" s="3">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="Y7" s="4">
+      <c r="Y7" s="3">
         <f t="shared" si="5"/>
         <v>62.5</v>
       </c>
@@ -1813,27 +1810,27 @@
       <c r="S8" s="3">
         <v>1</v>
       </c>
-      <c r="T8" s="4">
+      <c r="T8" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V8" s="3">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="W8" s="4">
+      <c r="W8" s="3">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="X8" s="4">
+      <c r="X8" s="3">
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="Y8" s="4">
+      <c r="Y8" s="3">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
@@ -1891,27 +1888,27 @@
       <c r="S9" s="3">
         <v>1</v>
       </c>
-      <c r="T9" s="4">
+      <c r="T9" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9" s="3">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="W9" s="4">
+      <c r="W9" s="3">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="X9" s="4">
+      <c r="X9" s="3">
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="Y9" s="4">
+      <c r="Y9" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
@@ -1969,27 +1966,27 @@
       <c r="S10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T10" s="4">
+      <c r="T10" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="V10" s="4">
+      <c r="V10" s="3">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="W10" s="4">
+      <c r="W10" s="3">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="X10" s="4">
+      <c r="X10" s="3">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="Y10" s="4">
+      <c r="Y10" s="3">
         <f t="shared" si="5"/>
         <v>62.5</v>
       </c>
@@ -2047,27 +2044,27 @@
       <c r="S11" s="3">
         <v>5</v>
       </c>
-      <c r="T11" s="4">
+      <c r="T11" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="U11" s="4">
+      <c r="U11" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="V11" s="4">
+      <c r="V11" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="W11" s="4">
+      <c r="W11" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="X11" s="4">
+      <c r="X11" s="3">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="Y11" s="4">
+      <c r="Y11" s="3">
         <f t="shared" si="5"/>
         <v>27.5</v>
       </c>
@@ -2125,27 +2122,27 @@
       <c r="S12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T12" s="4">
+      <c r="T12" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="V12" s="4">
+      <c r="V12" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="W12" s="4">
+      <c r="W12" s="3">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="X12" s="4">
+      <c r="X12" s="3">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="Y12" s="4">
+      <c r="Y12" s="3">
         <f t="shared" si="5"/>
         <v>65</v>
       </c>
@@ -2203,27 +2200,27 @@
       <c r="S13" s="3">
         <v>1</v>
       </c>
-      <c r="T13" s="4">
+      <c r="T13" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="U13" s="4">
+      <c r="U13" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="V13" s="4">
+      <c r="V13" s="3">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="W13" s="4">
+      <c r="W13" s="3">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="X13" s="4">
+      <c r="X13" s="3">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="Y13" s="4">
+      <c r="Y13" s="3">
         <f t="shared" si="5"/>
         <v>77.5</v>
       </c>
@@ -2281,27 +2278,27 @@
       <c r="S14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T14" s="4">
+      <c r="T14" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="U14" s="4">
+      <c r="U14" s="3">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="V14" s="4">
+      <c r="V14" s="3">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="W14" s="4">
+      <c r="W14" s="3">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="X14" s="4">
+      <c r="X14" s="3">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="Y14" s="4">
+      <c r="Y14" s="3">
         <f t="shared" si="5"/>
         <v>70</v>
       </c>
@@ -2359,27 +2356,27 @@
       <c r="S15" s="3">
         <v>1</v>
       </c>
-      <c r="T15" s="4">
+      <c r="T15" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="U15" s="4">
+      <c r="U15" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="V15" s="4">
+      <c r="V15" s="3">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="W15" s="4">
+      <c r="W15" s="3">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="X15" s="4">
+      <c r="X15" s="3">
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="Y15" s="4">
+      <c r="Y15" s="3">
         <f t="shared" si="5"/>
         <v>92.5</v>
       </c>
@@ -2437,27 +2434,27 @@
       <c r="S16" s="3">
         <v>1</v>
       </c>
-      <c r="T16" s="4">
+      <c r="T16" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="U16" s="4">
+      <c r="U16" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="V16" s="4">
+      <c r="V16" s="3">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="W16" s="4">
+      <c r="W16" s="3">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="X16" s="4">
+      <c r="X16" s="3">
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="Y16" s="4">
+      <c r="Y16" s="3">
         <f t="shared" si="5"/>
         <v>92.5</v>
       </c>
@@ -2515,27 +2512,27 @@
       <c r="S17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T17" s="4">
+      <c r="T17" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="V17" s="4">
+      <c r="V17" s="3">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="W17" s="4">
+      <c r="W17" s="3">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="X17" s="4">
+      <c r="X17" s="3">
         <f t="shared" si="4"/>
         <v>34</v>
       </c>
-      <c r="Y17" s="4">
+      <c r="Y17" s="3">
         <f t="shared" si="5"/>
         <v>85</v>
       </c>
@@ -2593,27 +2590,27 @@
       <c r="S18" s="3">
         <v>1</v>
       </c>
-      <c r="T18" s="4">
+      <c r="T18" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="U18" s="4">
+      <c r="U18" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="V18" s="4">
+      <c r="V18" s="3">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="W18" s="4">
+      <c r="W18" s="3">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="X18" s="4">
+      <c r="X18" s="3">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="Y18" s="4">
+      <c r="Y18" s="3">
         <f t="shared" si="5"/>
         <v>77.5</v>
       </c>
@@ -2671,27 +2668,27 @@
       <c r="S19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T19" s="4">
+      <c r="T19" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="U19" s="4">
+      <c r="U19" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="V19" s="4">
+      <c r="V19" s="3">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="W19" s="4">
+      <c r="W19" s="3">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="X19" s="4">
+      <c r="X19" s="3">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="Y19" s="4">
+      <c r="Y19" s="3">
         <f t="shared" si="5"/>
         <v>70</v>
       </c>
@@ -3012,22 +3009,22 @@
       <c r="S40" s="3"/>
     </row>
     <row r="45" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="X45" s="5"/>
-      <c r="Y45" s="5"/>
-      <c r="Z45" s="5"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
     </row>
     <row r="46" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="X46" s="5"/>
-      <c r="Y46" s="5">
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4">
         <f>AVERAGE(Y2:Y45)</f>
         <v>76.388888888888886</v>
       </c>
-      <c r="Z46" s="5"/>
+      <c r="Z46" s="4"/>
     </row>
     <row r="47" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="X47" s="5"/>
-      <c r="Y47" s="5"/>
-      <c r="Z47" s="5"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3182,27 +3179,27 @@
       <c r="S2" s="3">
         <v>1</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="3">
         <f t="shared" ref="T2:T19" si="0">SUM(J2-1,L2-1,N2-1,P2-1,R2-1)</f>
         <v>14</v>
       </c>
-      <c r="U2" s="4">
+      <c r="U2" s="3">
         <f t="shared" ref="U2:U19" si="1">T2</f>
         <v>14</v>
       </c>
-      <c r="V2" s="4">
+      <c r="V2" s="3">
         <f t="shared" ref="V2:V19" si="2">SUM(5-K2,5-M2,5-O2,5-Q2,5-S2)</f>
         <v>14</v>
       </c>
-      <c r="W2" s="4">
+      <c r="W2" s="3">
         <f t="shared" ref="W2:W19" si="3">V2</f>
         <v>14</v>
       </c>
-      <c r="X2" s="4">
+      <c r="X2" s="3">
         <f t="shared" ref="X2:X19" si="4">SUM(U2,W2)</f>
         <v>28</v>
       </c>
-      <c r="Y2" s="4">
+      <c r="Y2" s="3">
         <f t="shared" ref="Y2:Y19" si="5">X2*2.5</f>
         <v>70</v>
       </c>
@@ -3260,27 +3257,27 @@
       <c r="S3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="4">
+      <c r="T3" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="U3" s="4">
+      <c r="U3" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="V3" s="4">
+      <c r="V3" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="W3" s="4">
+      <c r="W3" s="3">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="X3" s="4">
+      <c r="X3" s="3">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="Y3" s="4">
+      <c r="Y3" s="3">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
@@ -3338,27 +3335,27 @@
       <c r="S4" s="3">
         <v>1</v>
       </c>
-      <c r="T4" s="4">
+      <c r="T4" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="V4" s="4">
+      <c r="V4" s="3">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="W4" s="4">
+      <c r="W4" s="3">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="X4" s="4">
+      <c r="X4" s="3">
         <f t="shared" si="4"/>
         <v>38</v>
       </c>
-      <c r="Y4" s="4">
+      <c r="Y4" s="3">
         <f t="shared" si="5"/>
         <v>95</v>
       </c>
@@ -3416,27 +3413,27 @@
       <c r="S5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="U5" s="4">
+      <c r="U5" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="V5" s="4">
+      <c r="V5" s="3">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="W5" s="4">
+      <c r="W5" s="3">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="X5" s="4">
+      <c r="X5" s="3">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="Y5" s="4">
+      <c r="Y5" s="3">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
@@ -3494,27 +3491,27 @@
       <c r="S6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T6" s="4">
+      <c r="T6" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="V6" s="4">
+      <c r="V6" s="3">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="W6" s="4">
+      <c r="W6" s="3">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="X6" s="4">
+      <c r="X6" s="3">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="Y6" s="4">
+      <c r="Y6" s="3">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
@@ -3572,27 +3569,27 @@
       <c r="S7" s="3">
         <v>5</v>
       </c>
-      <c r="T7" s="4">
+      <c r="T7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V7" s="3">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="W7" s="4">
+      <c r="W7" s="3">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="X7" s="4">
+      <c r="X7" s="3">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="Y7" s="4">
+      <c r="Y7" s="3">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
@@ -3650,27 +3647,27 @@
       <c r="S8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T8" s="4">
+      <c r="T8" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V8" s="3">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="W8" s="4">
+      <c r="W8" s="3">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="X8" s="4">
+      <c r="X8" s="3">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="Y8" s="4">
+      <c r="Y8" s="3">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
@@ -3728,27 +3725,27 @@
       <c r="S9" s="3">
         <v>1</v>
       </c>
-      <c r="T9" s="4">
+      <c r="T9" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9" s="3">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="W9" s="4">
+      <c r="W9" s="3">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="X9" s="4">
+      <c r="X9" s="3">
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="Y9" s="4">
+      <c r="Y9" s="3">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
@@ -3806,27 +3803,27 @@
       <c r="S10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T10" s="4">
+      <c r="T10" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="3">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="V10" s="4">
+      <c r="V10" s="3">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="W10" s="4">
+      <c r="W10" s="3">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="X10" s="4">
+      <c r="X10" s="3">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="Y10" s="4">
+      <c r="Y10" s="3">
         <f t="shared" si="5"/>
         <v>65</v>
       </c>
@@ -3884,27 +3881,27 @@
       <c r="S11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T11" s="4">
+      <c r="T11" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U11" s="4">
+      <c r="U11" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="V11" s="4">
+      <c r="V11" s="3">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="W11" s="4">
+      <c r="W11" s="3">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="X11" s="4">
+      <c r="X11" s="3">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="Y11" s="4">
+      <c r="Y11" s="3">
         <f t="shared" si="5"/>
         <v>72.5</v>
       </c>
@@ -3962,27 +3959,27 @@
       <c r="S12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T12" s="4">
+      <c r="T12" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="V12" s="4">
+      <c r="V12" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="W12" s="4">
+      <c r="W12" s="3">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="X12" s="4">
+      <c r="X12" s="3">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="Y12" s="4">
+      <c r="Y12" s="3">
         <f t="shared" si="5"/>
         <v>72.5</v>
       </c>
@@ -4040,27 +4037,27 @@
       <c r="S13" s="3">
         <v>1</v>
       </c>
-      <c r="T13" s="4">
+      <c r="T13" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="U13" s="4">
+      <c r="U13" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="V13" s="4">
+      <c r="V13" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="W13" s="4">
+      <c r="W13" s="3">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="X13" s="4">
+      <c r="X13" s="3">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="Y13" s="4">
+      <c r="Y13" s="3">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
@@ -4118,27 +4115,27 @@
       <c r="S14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T14" s="4">
+      <c r="T14" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="U14" s="4">
+      <c r="U14" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="V14" s="4">
+      <c r="V14" s="3">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="W14" s="4">
+      <c r="W14" s="3">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="X14" s="4">
+      <c r="X14" s="3">
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
-      <c r="Y14" s="4">
+      <c r="Y14" s="3">
         <f t="shared" si="5"/>
         <v>67.5</v>
       </c>
@@ -4196,27 +4193,27 @@
       <c r="S15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T15" s="4">
+      <c r="T15" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="U15" s="4">
+      <c r="U15" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="V15" s="4">
+      <c r="V15" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="W15" s="4">
+      <c r="W15" s="3">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="X15" s="4">
+      <c r="X15" s="3">
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="Y15" s="4">
+      <c r="Y15" s="3">
         <f t="shared" si="5"/>
         <v>52.5</v>
       </c>
@@ -4274,27 +4271,27 @@
       <c r="S16" s="3">
         <v>1</v>
       </c>
-      <c r="T16" s="4">
+      <c r="T16" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U16" s="4">
+      <c r="U16" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="V16" s="4">
+      <c r="V16" s="3">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="W16" s="4">
+      <c r="W16" s="3">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="X16" s="4">
+      <c r="X16" s="3">
         <f t="shared" si="4"/>
         <v>39</v>
       </c>
-      <c r="Y16" s="4">
+      <c r="Y16" s="3">
         <f t="shared" si="5"/>
         <v>97.5</v>
       </c>
@@ -4352,27 +4349,27 @@
       <c r="S17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T17" s="4">
+      <c r="T17" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="V17" s="4">
+      <c r="V17" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="W17" s="4">
+      <c r="W17" s="3">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="X17" s="4">
+      <c r="X17" s="3">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="Y17" s="4">
+      <c r="Y17" s="3">
         <f t="shared" si="5"/>
         <v>72.5</v>
       </c>
@@ -4430,27 +4427,27 @@
       <c r="S18" s="3">
         <v>1</v>
       </c>
-      <c r="T18" s="4">
+      <c r="T18" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U18" s="4">
+      <c r="U18" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="V18" s="4">
+      <c r="V18" s="3">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="W18" s="4">
+      <c r="W18" s="3">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="X18" s="4">
+      <c r="X18" s="3">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="Y18" s="4">
+      <c r="Y18" s="3">
         <f t="shared" si="5"/>
         <v>82.5</v>
       </c>
@@ -4508,27 +4505,27 @@
       <c r="S19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T19" s="4">
+      <c r="T19" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="U19" s="4">
+      <c r="U19" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="V19" s="4">
+      <c r="V19" s="3">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="W19" s="4">
+      <c r="W19" s="3">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="X19" s="4">
+      <c r="X19" s="3">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="Y19" s="4">
+      <c r="Y19" s="3">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
@@ -4849,22 +4846,22 @@
       <c r="S40" s="3"/>
     </row>
     <row r="45" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="X45" s="5"/>
-      <c r="Y45" s="5"/>
-      <c r="Z45" s="5"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
     </row>
     <row r="46" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="X46" s="5"/>
-      <c r="Y46" s="5">
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4">
         <f>AVERAGE(Y2:Y45)</f>
         <v>65.416666666666671</v>
       </c>
-      <c r="Z46" s="5"/>
+      <c r="Z46" s="4"/>
     </row>
     <row r="47" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="X47" s="5"/>
-      <c r="Y47" s="5"/>
-      <c r="Z47" s="5"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5019,27 +5016,27 @@
       <c r="S2" s="3">
         <v>1</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="3">
         <f t="shared" ref="T2:T19" si="0">SUM(J2-1,L2-1,N2-1,P2-1,R2-1)</f>
         <v>15</v>
       </c>
-      <c r="U2" s="4">
+      <c r="U2" s="3">
         <f t="shared" ref="U2:U19" si="1">T2</f>
         <v>15</v>
       </c>
-      <c r="V2" s="4">
+      <c r="V2" s="3">
         <f t="shared" ref="V2:V19" si="2">SUM(5-K2,5-M2,5-O2,5-Q2,5-S2)</f>
         <v>18</v>
       </c>
-      <c r="W2" s="4">
+      <c r="W2" s="3">
         <f t="shared" ref="W2:W19" si="3">V2</f>
         <v>18</v>
       </c>
-      <c r="X2" s="4">
+      <c r="X2" s="3">
         <f t="shared" ref="X2:X19" si="4">SUM(U2,W2)</f>
         <v>33</v>
       </c>
-      <c r="Y2" s="4">
+      <c r="Y2" s="3">
         <f t="shared" ref="Y2:Y19" si="5">X2*2.5</f>
         <v>82.5</v>
       </c>
@@ -5097,27 +5094,27 @@
       <c r="S3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="4">
+      <c r="T3" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="U3" s="4">
+      <c r="U3" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="V3" s="4">
+      <c r="V3" s="3">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="W3" s="4">
+      <c r="W3" s="3">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="X3" s="4">
+      <c r="X3" s="3">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="Y3" s="4">
+      <c r="Y3" s="3">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
@@ -5175,27 +5172,27 @@
       <c r="S4" s="3">
         <v>1</v>
       </c>
-      <c r="T4" s="4">
+      <c r="T4" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="V4" s="4">
+      <c r="V4" s="3">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="W4" s="4">
+      <c r="W4" s="3">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="X4" s="4">
+      <c r="X4" s="3">
         <f t="shared" si="4"/>
         <v>38</v>
       </c>
-      <c r="Y4" s="4">
+      <c r="Y4" s="3">
         <f t="shared" si="5"/>
         <v>95</v>
       </c>
@@ -5253,27 +5250,27 @@
       <c r="S5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U5" s="4">
+      <c r="U5" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="V5" s="4">
+      <c r="V5" s="3">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="W5" s="4">
+      <c r="W5" s="3">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="X5" s="4">
+      <c r="X5" s="3">
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="Y5" s="4">
+      <c r="Y5" s="3">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
@@ -5331,27 +5328,27 @@
       <c r="S6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="4">
+      <c r="T6" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="3">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="V6" s="4">
+      <c r="V6" s="3">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="W6" s="4">
+      <c r="W6" s="3">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="X6" s="4">
+      <c r="X6" s="3">
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="Y6" s="4">
+      <c r="Y6" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
@@ -5409,27 +5406,27 @@
       <c r="S7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T7" s="4">
+      <c r="T7" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V7" s="3">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="W7" s="4">
+      <c r="W7" s="3">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="X7" s="4">
+      <c r="X7" s="3">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="Y7" s="4">
+      <c r="Y7" s="3">
         <f t="shared" si="5"/>
         <v>77.5</v>
       </c>
@@ -5487,27 +5484,27 @@
       <c r="S8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T8" s="4">
+      <c r="T8" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V8" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="W8" s="4">
+      <c r="W8" s="3">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="X8" s="4">
+      <c r="X8" s="3">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="Y8" s="4">
+      <c r="Y8" s="3">
         <f t="shared" si="5"/>
         <v>57.5</v>
       </c>
@@ -5565,27 +5562,27 @@
       <c r="S9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="4">
+      <c r="T9" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="W9" s="4">
+      <c r="W9" s="3">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="X9" s="4">
+      <c r="X9" s="3">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="Y9" s="4">
+      <c r="Y9" s="3">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
@@ -5643,27 +5640,27 @@
       <c r="S10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T10" s="4">
+      <c r="T10" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="3">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="V10" s="4">
+      <c r="V10" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="W10" s="4">
+      <c r="W10" s="3">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="X10" s="4">
+      <c r="X10" s="3">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="Y10" s="4">
+      <c r="Y10" s="3">
         <f t="shared" si="5"/>
         <v>70</v>
       </c>
@@ -5721,27 +5718,27 @@
       <c r="S11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T11" s="4">
+      <c r="T11" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="U11" s="4">
+      <c r="U11" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="V11" s="4">
+      <c r="V11" s="3">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="W11" s="4">
+      <c r="W11" s="3">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="X11" s="4">
+      <c r="X11" s="3">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="Y11" s="4">
+      <c r="Y11" s="3">
         <f t="shared" si="5"/>
         <v>27.5</v>
       </c>
@@ -5799,27 +5796,27 @@
       <c r="S12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T12" s="4">
+      <c r="T12" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="V12" s="4">
+      <c r="V12" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="W12" s="4">
+      <c r="W12" s="3">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="X12" s="4">
+      <c r="X12" s="3">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="Y12" s="4">
+      <c r="Y12" s="3">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
@@ -5877,27 +5874,27 @@
       <c r="S13" s="3">
         <v>1</v>
       </c>
-      <c r="T13" s="4">
+      <c r="T13" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U13" s="4">
+      <c r="U13" s="3">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="V13" s="4">
+      <c r="V13" s="3">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="W13" s="4">
+      <c r="W13" s="3">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="X13" s="4">
+      <c r="X13" s="3">
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
-      <c r="Y13" s="4">
+      <c r="Y13" s="3">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
@@ -5955,27 +5952,27 @@
       <c r="S14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T14" s="4">
+      <c r="T14" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="U14" s="4">
+      <c r="U14" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="V14" s="4">
+      <c r="V14" s="3">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="W14" s="4">
+      <c r="W14" s="3">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="X14" s="4">
+      <c r="X14" s="3">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="Y14" s="4">
+      <c r="Y14" s="3">
         <f t="shared" si="5"/>
         <v>65</v>
       </c>
@@ -6033,27 +6030,27 @@
       <c r="S15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T15" s="4">
+      <c r="T15" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="U15" s="4">
+      <c r="U15" s="3">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="V15" s="4">
+      <c r="V15" s="3">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="W15" s="4">
+      <c r="W15" s="3">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="X15" s="4">
+      <c r="X15" s="3">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="Y15" s="4">
+      <c r="Y15" s="3">
         <f t="shared" si="5"/>
         <v>82.5</v>
       </c>
@@ -6111,27 +6108,27 @@
       <c r="S16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T16" s="4">
+      <c r="T16" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="U16" s="4">
+      <c r="U16" s="3">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="V16" s="4">
+      <c r="V16" s="3">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="W16" s="4">
+      <c r="W16" s="3">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="X16" s="4">
+      <c r="X16" s="3">
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="Y16" s="4">
+      <c r="Y16" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
@@ -6189,27 +6186,27 @@
       <c r="S17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T17" s="4">
+      <c r="T17" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17" s="3">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="V17" s="4">
+      <c r="V17" s="3">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="W17" s="4">
+      <c r="W17" s="3">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="X17" s="4">
+      <c r="X17" s="3">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="Y17" s="4">
+      <c r="Y17" s="3">
         <f t="shared" si="5"/>
         <v>82.5</v>
       </c>
@@ -6261,33 +6258,35 @@
       <c r="Q18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R18" s="3"/>
+      <c r="R18" s="3">
+        <v>4</v>
+      </c>
       <c r="S18" s="3">
         <v>1</v>
       </c>
-      <c r="T18" s="4">
+      <c r="T18" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="U18" s="4">
+        <v>15</v>
+      </c>
+      <c r="U18" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="V18" s="4">
+        <v>15</v>
+      </c>
+      <c r="V18" s="3">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="W18" s="4">
+      <c r="W18" s="3">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="X18" s="4">
+      <c r="X18" s="3">
         <f t="shared" si="4"/>
-        <v>28</v>
-      </c>
-      <c r="Y18" s="4">
+        <v>32</v>
+      </c>
+      <c r="Y18" s="3">
         <f t="shared" si="5"/>
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
@@ -6343,27 +6342,27 @@
       <c r="S19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T19" s="4">
+      <c r="T19" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="U19" s="4">
+      <c r="U19" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="V19" s="4">
+      <c r="V19" s="3">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="W19" s="4">
+      <c r="W19" s="3">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="X19" s="4">
+      <c r="X19" s="3">
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="Y19" s="4">
+      <c r="Y19" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
@@ -6684,22 +6683,22 @@
       <c r="S40" s="3"/>
     </row>
     <row r="45" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="X45" s="5"/>
-      <c r="Y45" s="5"/>
-      <c r="Z45" s="5"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
     </row>
     <row r="46" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="X46" s="5"/>
-      <c r="Y46" s="5">
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4">
         <f>AVERAGE(Y2:Y45)</f>
-        <v>71.388888888888886</v>
-      </c>
-      <c r="Z46" s="5"/>
+        <v>71.944444444444443</v>
+      </c>
+      <c r="Z46" s="4"/>
     </row>
     <row r="47" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="X47" s="5"/>
-      <c r="Y47" s="5"/>
-      <c r="Z47" s="5"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8768,7 +8767,9 @@
       <c r="AK18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AL18" s="3"/>
+      <c r="AL18" s="3">
+        <v>4</v>
+      </c>
       <c r="AM18" s="3">
         <v>1</v>
       </c>
@@ -9660,7 +9661,7 @@
       </c>
       <c r="B3">
         <f>'SUS Proxmox'!Y46</f>
-        <v>71.388888888888886</v>
+        <v>71.944444444444443</v>
       </c>
     </row>
   </sheetData>
